--- a/artfynd/Jordbro naturreservat artfynd.xlsx
+++ b/artfynd/Jordbro naturreservat artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862317</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127893550</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1036,6 +1051,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77924066</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59442899</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1260,6 +1285,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5952788</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1365,6 +1395,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87653504</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1488,6 +1523,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119732223</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1606,6 +1646,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77924125</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1725,6 +1770,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133834436</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1845,6 +1895,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134365757</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1964,6 +2019,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134351415</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2068,6 +2128,11 @@
       <c r="AY13" t="inlineStr">
         <is>
           <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2698620</t>
         </is>
       </c>
     </row>
@@ -2177,6 +2242,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107269897</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2282,6 +2352,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71731553</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2382,6 +2457,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71731739</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2482,6 +2562,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71731792</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2582,6 +2667,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71731665</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2682,6 +2772,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71732366</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2788,6 +2883,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/337353</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2894,6 +2994,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1513267</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3000,6 +3105,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1551771</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3106,6 +3216,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1551772</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3241,8 +3356,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108032321</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>